--- a/static/data/exports/Retro_AS_AE_2021.xlsx
+++ b/static/data/exports/Retro_AS_AE_2021.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Retro Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Retro Data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/static/data/exports/Retro_AS_AE_2021.xlsx
+++ b/static/data/exports/Retro_AS_AE_2021.xlsx
@@ -5739,11 +5739,11 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>1719170</v>
+        <v>1719169</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Wahidul Islam Choudhury</t>
+          <t>Abul Hussain Barbhuiya</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -5776,7 +5776,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>Wahidul Islam Choudhury</t>
+          <t>Abul Hussain Barbhuiya</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -5785,7 +5785,7 @@
         </is>
       </c>
       <c r="Q86" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R86" t="n">
         <v>42</v>
@@ -5801,11 +5801,11 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>1719169</v>
+        <v>1719170</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Abul Hussain Barbhuiya</t>
+          <t>Wahidul Islam Choudhury</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -5838,7 +5838,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>Abul Hussain Barbhuiya</t>
+          <t>Wahidul Islam Choudhury</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -5847,7 +5847,7 @@
         </is>
       </c>
       <c r="Q87" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R87" t="n">
         <v>42</v>
@@ -16651,20 +16651,20 @@
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>1719345</v>
+        <v>1719346</v>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Nota</t>
+          <t>Abdur Rezzak Hossain</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>NOTA</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D262" t="n">
-        <v>19863</v>
+        <v>19861</v>
       </c>
       <c r="E262" t="n">
         <v>1758</v>
@@ -16688,16 +16688,16 @@
       </c>
       <c r="K262" t="inlineStr">
         <is>
-          <t>Nota</t>
+          <t>Abdur Rezzak Hossain</t>
         </is>
       </c>
       <c r="L262" t="inlineStr">
         <is>
-          <t>NOTA</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="Q262" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R262" t="n">
         <v>42</v>
@@ -16713,20 +16713,20 @@
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>1719346</v>
+        <v>1719345</v>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Abdur Rezzak Hossain</t>
+          <t>Nota</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>NOTA</t>
         </is>
       </c>
       <c r="D263" t="n">
-        <v>19861</v>
+        <v>19863</v>
       </c>
       <c r="E263" t="n">
         <v>1758</v>
@@ -16750,16 +16750,16 @@
       </c>
       <c r="K263" t="inlineStr">
         <is>
-          <t>Abdur Rezzak Hossain</t>
+          <t>Nota</t>
         </is>
       </c>
       <c r="L263" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>NOTA</t>
         </is>
       </c>
       <c r="Q263" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R263" t="n">
         <v>42</v>
